--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92379</v>
+        <v>92381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92381</v>
+        <v>92383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92392</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92398</v>
+        <v>92411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92411</v>
+        <v>92413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92413</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35674-2026 artfynd.xlsx
+++ b/artfynd/A 35674-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136741565</v>
       </c>
       <c r="B2" t="n">
-        <v>92426</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136741566</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
